--- a/06-soc2-readiness-internal-audit/06-soc2-readiness-and-internal-audit.xlsx
+++ b/06-soc2-readiness-internal-audit/06-soc2-readiness-and-internal-audit.xlsx
@@ -146,7 +146,7 @@
     <t xml:space="preserve">GITHUB</t>
   </si>
   <si>
-    <t xml:space="preserve">Upload to grc-portfolio/06-soc2-readiness-internal-audit/. Create folders by typing 06-soc2-readiness-internal-audit/filename as the file path; GitHub has no 'new folder' button.</t>
+    <t xml:space="preserve">Upload to grc-portfolio/06-soc2-readiness-internal-audit/. Create folders by typing 06-soc2-readiness-internal-audit/filename as the file path; CodeCo has no 'new folder' button.</t>
   </si>
   <si>
     <t xml:space="preserve">NOTION</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">IN - mandatory</t>
   </si>
   <si>
-    <t xml:space="preserve">Required in every SOC 2 engagement. Carries R-001 phishing, R-002 ransomware, R-003 insider exfiltration, R-004 production API authorisation flaw and R-005 AWS misconfiguration, plus VR-001 to VR-009. Thirty-three criteria.</t>
+    <t xml:space="preserve">Required in every SOC 2 engagement. Carries R-001 phishing, R-002 ransomware, R-003 insider exfiltration, R-004 production API authorisation flaw and R-005 CloudCo misconfiguration, plus VR-001 to VR-009. Thirty-three criteria.</t>
   </si>
   <si>
     <t xml:space="preserve">Availability (A1)</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">IN - with a precondition</t>
   </si>
   <si>
-    <t xml:space="preserve">Approximately 200 customers run project delivery on the platform; unavailability is the loss they feel first. R-002 (ransomware) and VR-002 (five vendors sharing AWS with the platform) both carry availability impact, and CG-01 (backup, recovery and restore testing) is still open. PRECONDITION: A1 asks whether the system is available 'as committed'. Assumption ISO-A04 records that no contractual SLA figure exists anywhere in Projects 1-4. Service commitments must be published (SOC-05) before Availability can be included in a real engagement.</t>
+    <t xml:space="preserve">Approximately 200 customers run project delivery on the platform; unavailability is the loss they feel first. R-002 (ransomware) and VR-002 (five vendors sharing CloudCo with the platform) both carry availability impact, and CG-01 (backup, recovery and restore testing) is still open. PRECONDITION: A1 asks whether the system is available 'as committed'. Assumption ISO-A04 records that no contractual SLA figure exists anywhere in Projects 1-4. Service commitments must be published (SOC-05) before Availability can be included in a real engagement.</t>
   </si>
   <si>
     <t xml:space="preserve">Confidentiality (C1)</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">OUT</t>
   </si>
   <si>
-    <t xml:space="preserve">PI1 asks whether processing is complete, valid, accurate, timely and authorised. The platform manages project and task records that customers enter and control; it performs no calculation or transaction processing on their behalf, and payment processing belongs to Stripe (CGI-POL-004 s4.1.4 and AVD-001 confirm no card numbers are held). No risk in CGI-RSK-001 v1.1 concerns processing completeness or accuracy. Including PI1 would assert something no customer has asked for and no risk supports.</t>
+    <t xml:space="preserve">PI1 asks whether processing is complete, valid, accurate, timely and authorised. The platform manages project and task records that customers enter and control; it performs no calculation or transaction processing on their behalf, and payment processing belongs to PaymentsCo (CGI-POL-004 s4.1.4 and AVD-001 confirm no card numbers are held). No risk in CGI-RSK-001 v1.1 concerns processing completeness or accuracy. Including PI1 would assert something no customer has asked for and no risk supports.</t>
   </si>
   <si>
     <t xml:space="preserve">Privacy (P1-P8)</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">CC9.2 - vendor and business partner risk management</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS is carved out; without vendor controls the carve-out is a hole, not a boundary.</t>
+    <t xml:space="preserve">CloudCo is carved out; without vendor controls the carve-out is a hole, not a boundary.</t>
   </si>
   <si>
     <t xml:space="preserve">CC9.2 CRL 2, design Adequate</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">CC6.1, CC6.6</t>
   </si>
   <si>
-    <t xml:space="preserve">Part 3 - AWS is CARVED OUT. These are the controls the report relies on it to perform.</t>
+    <t xml:space="preserve">Part 3 - CloudCo is CARVED OUT. These are the controls the report relies on it to perform.</t>
   </si>
   <si>
     <t xml:space="preserve">CSOC ID</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">CSOC-01</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS (CGI-VEN-001)</t>
+    <t xml:space="preserve">CloudCo (CGI-VEN-001)</t>
   </si>
   <si>
     <t xml:space="preserve">Physical and environmental security of the data centres hosting the platform, including physical access control, monitoring, power and cooling.</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">A1.1, A1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">As CSOC-01. VR-002 records the concentration: five further vendors share AWS with the platform.</t>
+    <t xml:space="preserve">As CSOC-01. VR-002 records the concentration: five further vendors share CloudCo with the platform.</t>
   </si>
   <si>
     <t xml:space="preserve">CSOC-04</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">CC6.1, CC6.3</t>
   </si>
   <si>
-    <t xml:space="preserve">THE MIRROR: the CUECs CGI writes for its customers, against the CUECs AWS wrote for CGI</t>
+    <t xml:space="preserve">THE MIRROR: the CUECs CGI writes for its customers, against the CUECs CloudCo wrote for CGI</t>
   </si>
   <si>
     <t xml:space="preserve">CGI CUEC written for its customers</t>
   </si>
   <si>
-    <t xml:space="preserve">The AWS CUEC it mirrors</t>
+    <t xml:space="preserve">The CloudCo CUEC it mirrors</t>
   </si>
   <si>
     <t xml:space="preserve">CGI's own status as a customer</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">CUEC-02 - customers must enable MFA, phishing-resistant for administrators</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS CUEC 2 - MFA on the root account and restricted root use</t>
+    <t xml:space="preserve">CloudCo CUEC 2 - MFA on the root account and restricted root use</t>
   </si>
   <si>
     <t xml:space="preserve">UNACCEPTED. F-010; no owner assigned; condition C1 open until 15 Dec 2026.</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">CUEC-03 - customers must review their users' access at least quarterly</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS CUEC 3 - least-privilege IAM with periodic review</t>
+    <t xml:space="preserve">CloudCo CUEC 3 - least-privilege IAM with periodic review</t>
   </si>
   <si>
     <t xml:space="preserve">NEVER PERFORMED. CGI-POL-003 s4.7.1 mandates a quarterly privileged review; zero have run (OFI-15).</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">CUEC-05 - customers must review the tenant audit log and report anomalies</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS CUEC 1 - organisation-wide CloudTrail with log file validation</t>
+    <t xml:space="preserve">CloudCo CUEC 1 - organisation-wide CloudTrail with log file validation</t>
   </si>
   <si>
     <t xml:space="preserve">UNVERIFIED. No central security log account, no retention standard, no alert rules (OFI-03).</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">CUEC-07 - customers are responsible for classifying the data they upload</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS CUEC 4 - encryption management for customer-controlled data</t>
+    <t xml:space="preserve">CloudCo CUEC 4 - encryption management for customer-controlled data</t>
   </si>
   <si>
     <t xml:space="preserve">NO STANDARD. CGI-POL-004 says where encryption is required; no algorithms, TLS minimum or key management exist.</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">1. Inspect the documented method (NIST SP 800-30 Rev. 1 5x5, thresholds). 2. Test for risk acceptance criteria. 3. Trace ACC-001 and ACC-V01 to the criteria they were accepted against. 4. Re-perform the scoring of two risks. 5. Test whether fraud was considered (informs the SOC 2 overlay, CC3.3).</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-RSK-001 v1.1 methodology and thresholds (Low 1-4 / Medium 5-9 / High 10-14 / Critical 15-25); ACC-001 (SMS MFA, expires 03 Mar 2027); ACC-V01 (Calendly, expires 15 Sep 2028)</t>
+    <t xml:space="preserve">CGI-RSK-001 v1.1 methodology and thresholds (Low 1-4 / Medium 5-9 / High 10-14 / Critical 15-25); ACC-001 (SMS MFA, expires 03 Mar 2027); ACC-V01 (SchedulerCo, expires 15 Sep 2028)</t>
   </si>
   <si>
     <t xml:space="preserve">PARTIAL - the assessment and analysis method is documented and consistently applied. Acceptance criteria are absent.</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">1. Obtain the joiner/mover/leaver population and reconcile it to HR records. 2. Select leavers and test revocation against the four-hour SLA. 3. Test all quarterly privileged access reviews in the period. 4. Test MFA enrolment against the 100% requirement and against ACC-001.</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-POL-003 v1.0; CGI-TRK-001 (80% MFA enrolled); ACC-001 accepting SMS MFA until 03 Mar 2027; CGI-TPR-001 F-003 (no SCIM on Slack, manual leaver removal); one account (Lena Fischer) correctly not yet created under CGI-POL-003 s4.3.3</t>
+    <t xml:space="preserve">CGI-POL-003 v1.0; CGI-TRK-001 (80% MFA enrolled); ACC-001 accepting SMS MFA until 03 Mar 2027; CGI-TPR-001 F-003 (no SCIM on ChatCo, manual leaver removal); one account (Lena Fischer) correctly not yet created under CGI-POL-003 s4.3.3</t>
   </si>
   <si>
     <t xml:space="preserve">PARTIAL - CGI-POL-003 is an approved and complete access control design. It cannot be met on the four non-federated vendors (F-003).</t>
@@ -3020,16 +3020,16 @@
     <t xml:space="preserve">Attribute testing; stratified selection, census of the highest tier</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Test each sampled vendor for tier, assessment, DPA, assurance artifact and review date. 2. Test the review cadence (12/18/24 months) for reviews actually performed. 3. Test the AWS CUEC acceptance record. 4. Test the sub-processor change feed subscription.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CGI-TPR-001 v1.0; CGI-TPR-002 (74 questions, 16 domains); VRA-2026-001 AWS PASS WITH CONDITIONS 89%; VRA-2026-002 Slack FAIL 65%; VRA-2026-003 Calendly ACCEPTED 92%; findings F-001 to F-013</t>
+    <t xml:space="preserve">1. Test each sampled vendor for tier, assessment, DPA, assurance artifact and review date. 2. Test the review cadence (12/18/24 months) for reviews actually performed. 3. Test the CloudCo CUEC acceptance record. 4. Test the sub-processor change feed subscription.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGI-TPR-001 v1.0; CGI-TPR-002 (74 questions, 16 domains); VRA-2026-001 CloudCo PASS WITH CONDITIONS 89%; VRA-2026-002 ChatCo FAIL 65%; VRA-2026-003 SchedulerCo ACCEPTED 92%; findings F-001 to F-013</t>
   </si>
   <si>
     <t xml:space="preserve">PASS - the programme is designed, owned and communicated: tiering model, questionnaire, onboarding gates, 18-clause contract checklist, review cadence.</t>
   </si>
   <si>
-    <t xml:space="preserve">FAIL - zero scheduled reviews have been performed; the first Tier 1 re-reviews fall due Sep 2027. The four AWS CUECs are unaccepted. No sub-processor change feed is subscribed. Slack has operated in FAIL status since 15 Sep 2026 with no expiring risk acceptance on file.</t>
+    <t xml:space="preserve">FAIL - zero scheduled reviews have been performed; the first Tier 1 re-reviews fall due Sep 2027. The four CloudCo CUECs are unaccepted. No sub-processor change feed is subscribed. ChatCo has operated in FAIL status since 15 Sep 2026 with no expiring risk acceptance on file.</t>
   </si>
   <si>
     <t xml:space="preserve">Designed, not cycled. This is the clearest example in the ISMS of the difference between a control that exists and a control that operates.</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">1. For each of the 17 vendors, inspect for an executed DPA. 2. Test whether personal data is in fact processed. 3. Request the GDPR Article 30 record of processing activities. 4. Test for a transfer register covering non-EEA processing.</t>
   </si>
   <si>
-    <t xml:space="preserve">11 executed DPAs; 6 vendors with none (KRI-V1 = 65%); CGI-TPR-001 F-001 (Slack: no DPA, US-hosted), F-004, O-001; no Article 30 record exists</t>
+    <t xml:space="preserve">11 executed DPAs; 6 vendors with none (KRI-V1 = 65%); CGI-TPR-001 F-001 (ChatCo: no DPA, US-hosted), F-004, O-001; no Article 30 record exists</t>
   </si>
   <si>
     <t xml:space="preserve">PARTIAL - CGI-TPR-001 Gate B forbids onboarding without a DPA. The gate was built after the six were onboarded.</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">1. Inspect CGI-POL-005 for severity bands, roles, targets and reporting channels. 2. Walk through a hypothetical SEV1 with the CTO. 3. Request incident register entries. 4. Request the tabletop exercise record and lessons learned.</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-POL-005 v1.0 with SEV1-SEV4, s5.2 reporting channels, s5.5 response stages, s5.6.3 GDPR 72-hour duty, s5.7 review; CGI-TPR-001 F-002 (no vendor breach-notification clause), F-008 (no tenant audit log on Slack)</t>
+    <t xml:space="preserve">CGI-POL-005 v1.0 with SEV1-SEV4, s5.2 reporting channels, s5.5 response stages, s5.6.3 GDPR 72-hour duty, s5.7 review; CGI-TPR-001 F-002 (no vendor breach-notification clause), F-008 (no tenant audit log on ChatCo)</t>
   </si>
   <si>
     <t xml:space="preserve">PASS with exceptions - the plan is approved and complete on severity, roles and targets. No containment runbooks exist and no out-of-band communication channel is named.</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">Inspection of configuration; inquiry; attempted re-performance</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Inspect the AWS snapshot configuration and schedule. 2. Request declared RTO and RPO. 3. Request restore test reports for the period. 4. Request evidence that the data export path has been exercised.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS native snapshots configured (eu-central-1 primary, us-east-1 backup copies); CGI-TPR-001 F-013 (no RTO, no RPO, no restore test, export never exercised); VRA-2026-001 condition C4 due 15 Dec 2026</t>
+    <t xml:space="preserve">1. Inspect the CloudCo snapshot configuration and schedule. 2. Request declared RTO and RPO. 3. Request restore test reports for the period. 4. Request evidence that the data export path has been exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudCo native snapshots configured (eu-central-1 primary, us-east-1 backup copies); CGI-TPR-001 F-013 (no RTO, no RPO, no restore test, export never exercised); VRA-2026-001 condition C4 due 15 Dec 2026</t>
   </si>
   <si>
     <t xml:space="preserve">FAIL - no CGI-POL-006, no declared recovery objectives, no test schedule. A backup with no restore test and no objective is an assumption, not a control.</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">Attempted population construction; inspection of repository configuration; inquiry of the CTO</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Request the change record or release log for the period. 2. Request the GitHub branch-protection configuration export. 3. Request scan reports and remediation tickets. 4. Request the penetration test report. 5. Request the environment separation diagram.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CGI-POL-002 s4.5.2 secret scanning (a fragment); CGI-VEN-002 GitHub Tier 1, inherent 15 Critical, no branch protection on the CGI side; CGI-GAP-001 PR.PS = 0</t>
+    <t xml:space="preserve">1. Request the change record or release log for the period. 2. Request the CodeCo branch-protection configuration export. 3. Request scan reports and remediation tickets. 4. Request the penetration test report. 5. Request the environment separation diagram.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGI-POL-002 s4.5.2 secret scanning (a fragment); CGI-VEN-002 CodeCo Tier 1, inherent 15 Critical, no branch protection on the CGI side; CGI-GAP-001 PR.PS = 0</t>
   </si>
   <si>
     <t xml:space="preserve">FAIL - CGI-POL-007 and CGI-POL-008 are unwritten. There is no coding standard, no mandatory peer review, no scanning SLA and no recorded environment separation.</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">Inquiry of the IT Operations Manager; CGI-TPR-001 F-010; CGI-GAP-001 PR.IR = 0, DE.CM = 1</t>
   </si>
   <si>
-    <t xml:space="preserve">0 baselines; 4 AWS CUECs (100%)</t>
+    <t xml:space="preserve">0 baselines; 4 CloudCo CUECs (100%)</t>
   </si>
   <si>
     <t xml:space="preserve">Inquiry; inspection of available configuration; attribute testing of the four CUECs</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Request the AWS configuration baseline. 2. Request drift-detection or posture reports. 3. Test each of the four AWS CUECs for acceptance and an assigned owner. 4. Request CloudTrail configuration with log file validation. 5. Request alert rules and handled-alert records.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VRA-2026-001 F-010: four unaccepted CUECs (organisation-wide CloudTrail with log file validation; MFA on the root account with restricted root use; least-privilege IAM with periodic review; encryption management for customer-controlled data); Datadog APM used for engineering, not as a security log source</t>
+    <t xml:space="preserve">1. Request the CloudCo configuration baseline. 2. Request drift-detection or posture reports. 3. Test each of the four CloudCo CUECs for acceptance and an assigned owner. 4. Request CloudTrail configuration with log file validation. 5. Request alert rules and handled-alert records.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VRA-2026-001 F-010: four unaccepted CUECs (organisation-wide CloudTrail with log file validation; MFA on the root account with restricted root use; least-privilege IAM with periodic review; encryption management for customer-controlled data); MonitorCo APM used for engineering, not as a security log source</t>
   </si>
   <si>
     <t xml:space="preserve">FAIL - no baseline, no drift detection, no alert rules and no central security log account exist.</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">FAIL on the CUECs: 0 of 4 accepted and assigned. NOT PERFORMED elsewhere - population zero.</t>
   </si>
   <si>
-    <t xml:space="preserve">R-005 stays High for exactly this reason: the gap sits on the organisation's side of the shared-responsibility boundary, where no provider certificate reaches. Condition C1 is due 15 December 2026; if it is not met, the AWS conditional pass lapses to Fail.</t>
+    <t xml:space="preserve">R-005 stays High for exactly this reason: the gap sits on the organisation's side of the shared-responsibility boundary, where no provider certificate reaches. Condition C1 is due 15 December 2026; if it is not met, the CloudCo conditional pass lapses to Fail.</t>
   </si>
   <si>
     <t xml:space="preserve">OFI-03; OFI-07</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">1. Request the asset and SaaS inventory. 2. Test whether the four CGI-POL-004 tiers have been applied to any asset. 3. Request the endpoint register for the 50 BYOD devices. 4. Request retention/deletion records and DLP alert samples.</t>
   </si>
   <si>
-    <t xml:space="preserve">CGI-POL-004 v1.0 four tiers and Handling Matrix (approved, never applied); EXC-003 (Restricted data on removable media); CGI-VEN-007 Datadog log scrubbing rules unverified</t>
+    <t xml:space="preserve">CGI-POL-004 v1.0 four tiers and Handling Matrix (approved, never applied); EXC-003 (Restricted data on removable media); CGI-VEN-007 MonitorCo log scrubbing rules unverified</t>
   </si>
   <si>
     <t xml:space="preserve">PARTIAL - the classification scheme and handling matrix are approved and complete. No inventory exists for them to be applied to, and no DLP capability is designed.</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">The scope statement is complete and names interfaces and dependencies, but has not been approved by top management. This escalates to a major nonconformity if it is still unapproved at Stage 1.</t>
   </si>
   <si>
-    <t xml:space="preserve">Approve the ISMS scope and boundary, including the AWS shared-responsibility statement.</t>
+    <t xml:space="preserve">Approve the ISMS scope and boundary, including the CloudCo shared-responsibility statement.</t>
   </si>
   <si>
     <t xml:space="preserve">ISO-02</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">Backups have never been restore-tested and no RTO or RPO is declared</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS snapshots are configured. No restore has been performed, no recovery objectives are declared and the data export path has never been exercised. The SoA target date is 15 Dec 2026 and has not passed, so this is not yet a nonconformity. It becomes one on 16 Dec 2026.</t>
+    <t xml:space="preserve">CloudCo snapshots are configured. No restore has been performed, no recovery objectives are declared and the data export path has never been exercised. The SoA target date is 15 Dec 2026 and has not passed, so this is not yet a nonconformity. It becomes one on 16 Dec 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">IT Operations Manager</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">No baseline, no posture monitoring, no network security baseline and no documented segmentation. This is the documented reason R-005 remains High.</t>
   </si>
   <si>
-    <t xml:space="preserve">Implement a CIS AWS Foundations baseline with posture monitoring (Project 7 delivers this).</t>
+    <t xml:space="preserve">Implement a CIS CloudCo Foundations baseline with posture monitoring (Project 7 delivers this).</t>
   </si>
   <si>
     <t xml:space="preserve">REC-11</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">Monitoring is metadata-only. Retention limits are designed in CGI-POL-004 and have never been executed, and no masking exists for logs or lower environments.</t>
   </si>
   <si>
-    <t xml:space="preserve">Implement egress and DLP rules on Google Workspace and GitHub; execute the retention and deletion schedule.</t>
+    <t xml:space="preserve">Implement egress and DLP rules on OfficeCo and CodeCo; execute the retention and deletion schedule.</t>
   </si>
   <si>
     <t xml:space="preserve">REC-17</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">A.5.23; VRA-2026-001 C1</t>
   </si>
   <si>
-    <t xml:space="preserve">Four AWS complementary user entity controls are unaccepted</t>
+    <t xml:space="preserve">Four CloudCo complementary user entity controls are unaccepted</t>
   </si>
   <si>
     <t xml:space="preserve">Organisation-wide CloudTrail with log file validation, MFA on the root account with restricted root use, least-privilege IAM with periodic review, and encryption management are all assumed by the provider's report and performed by nobody. If C1 is not met by 15 Dec 2026 the conditional pass lapses to Fail.</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">A Tier 1 vendor is operating in FAIL status with no risk acceptance</t>
   </si>
   <si>
-    <t xml:space="preserve">Slack (CGI-VEN-004) scored 65% and failed on 15 Sep 2026. No CEO-approved, expiring risk acceptance on the ACC-001 pattern is on file. Re-assessment is due 15 Dec 2026.</t>
+    <t xml:space="preserve">ChatCo (CGI-VEN-004) scored 65% and failed on 15 Sep 2026. No CEO-approved, expiring risk acceptance on the ACC-001 pattern is on file. Re-assessment is due 15 Dec 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Remediate to a pass, or record a CEO-approved expiring acceptance, before Stage 1.</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">No compliance checking and no procedures beneath the policies</t>
   </si>
   <si>
-    <t xml:space="preserve">No compliance check against policy has ever run, and the runbooks the policies rely on do not exist. The planned runbook location shares AWS with the platform it would be used to recover.</t>
+    <t xml:space="preserve">No compliance check against policy has ever run, and the runbooks the policies rely on do not exist. The planned runbook location shares CloudCo with the platform it would be used to recover.</t>
   </si>
   <si>
     <t xml:space="preserve">Add a quarterly compliance check to the management review agenda; write runbooks and store them outside the platform's own dependency.</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">Screenshot</t>
   </si>
   <si>
-    <t xml:space="preserve">Received - AWS snapshot configuration</t>
+    <t xml:space="preserve">Received - CloudCo snapshot configuration</t>
   </si>
   <si>
     <t xml:space="preserve">PBC-34</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">SOC-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Decide the report strategy and confirm the scope: Security + Availability + Confidentiality, AWS carved out, one system (the platform)</t>
+    <t xml:space="preserve">Decide the report strategy and confirm the scope: Security + Availability + Confidentiality, CloudCo carved out, one system (the platform)</t>
   </si>
   <si>
     <t xml:space="preserve">All</t>
@@ -4802,7 +4802,7 @@
     <t xml:space="preserve">Phase 4 - Sustain</t>
   </si>
   <si>
-    <t xml:space="preserve">The gap CGI itself found in a vendor (F-006, stale Slack SOC 2) - do not repeat it</t>
+    <t xml:space="preserve">The gap CGI itself found in a vendor (F-006, stale ChatCo SOC 2) - do not repeat it</t>
   </si>
   <si>
     <t xml:space="preserve">SOC 2-specific cost, planning estimate</t>
@@ -5680,169 +5680,251 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGI-SOC-001 / CGI-IAU-001</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOC 2 Type II Readiness Assessment and ISO 27001 Internal Audit Workpapers</t>
+        </is>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organisation</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cypher Group Inc. (SIMULATED) - 50 employees, B2B SaaS project-management platform, ~200 SMB customers</t>
+        </is>
       </c>
     </row>
     <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASE STUDY NOTICE</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cypher Group Inc. is a simulated company. Every finding, score, date, cost and figure was created to demonstrate applied GRC methodology. This is a portfolio artifact, not evidence of employment or of a real engagement.</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Criteria version</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AICPA 2017 Trust Services Criteria with the 2022 revised points of focus. Security (CC1-CC9), Availability (A1), Confidentiality (C1). Criteria wording is paraphrased; obtain the criteria from the AICPA.</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard version</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISO/IEC 27001:2022 including Amd 1:2024. Requirement wording is paraphrased; obtain the standard from ISO or a national body.</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prepared by</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O.S (assessor and internal auditor)</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approved by</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer</t>
+        </is>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25 September 2026</t>
+        </is>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inputs consumed</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGI-POL-001 to -005 v1.0 | CGI-TRK-001 | EXC-001 to -003 | CGI-RSK-001 v1.1 (14 risks) | CGI-GAP-001 v1.0 (as updated by Project 4) | CGI-TPR-001 / -002 (17 vendors) | CGI-ISO-001 v1.0 draft (93-control SoA)</t>
+        </is>
       </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>19</v>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INDEPENDENCE LIMITATION</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The auditor prepared CGI-ISO-001, including the Statement of Applicability tested in WP-06. ISO/IEC 27001 clause 9.2.2 c) requires auditor objectivity and impartiality. This engagement is therefore a DRY RUN: it delivers the method and the workpapers, not conformity with clause 9.2. See finding OFI-08.</t>
+        </is>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COLOUR LEGEND</t>
+        </is>
       </c>
       <c r="B11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>22</v>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Yellow</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User input - replace with your own data</t>
+        </is>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>24</v>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Grey</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula - do not overtype</t>
+        </is>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>26</v>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Green</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass / worked example</t>
+        </is>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>28</v>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Red</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fail / zero</t>
+        </is>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>30</v>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Amber</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial / conditional</t>
+        </is>
       </c>
     </row>
     <row r="17" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>32</v>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCORING METHOD</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Criterion Readiness Level (CRL) = mean of the mapped item maturities, banded: &lt;0.5=0, 0.5-1.49=1, 1.5-2.49=2, &gt;=2.5=3. Management-system requirements score 0-2 and convert 0-&gt;0, 1-&gt;2, 2-&gt;3. Design is Adequate only when CRL&gt;=2 AND no mapped control sits at maturity 0. Operating is Evidenced only at CRL 3. Type I readiness = SUM(MIN(CRL,2))/(38x2). Type II readiness = SUM(CRL)/(38x3). Gate override: any failed gate = NO-GO whatever the percentage.</t>
+        </is>
       </c>
     </row>
     <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>34</v>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HOW TO USE</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Replace 03_AnnexA_Maturity and 04_Clause_Readiness with your own assessment. 2. Adjust 02_Crosswalk_Map if your control set differs. 3. Everything on 01_TSC_Crosswalk, 06_Readiness_Score and 07_Gates recalculates. 4. Recalculate the whole workbook before you publish: LibreOffice Ctrl+Shift+F9, Excel Ctrl+Alt+F9.</t>
+        </is>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>36</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GITHUB</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload to grc-portfolio/06-soc2-readiness-internal-audit/. Create folders by typing 06-soc2-readiness-internal-audit/filename as the file path; GitHub has no 'new folder' button.</t>
+        </is>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>38</v>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOTION</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Import each data/*.csv as a database. Set Rating, Status, Design verdict and Owner to Select; CRL, Mean and Maturity to Number; dates to Date.</t>
+        </is>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>40</v>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16_Issue_Checklist must read PASS on every row before this workbook is published.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/06-soc2-readiness-internal-audit/06-soc2-readiness-and-internal-audit.xlsx
+++ b/06-soc2-readiness-internal-audit/06-soc2-readiness-and-internal-audit.xlsx
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">No baseline, no posture monitoring, no network security baseline and no documented segmentation. This is the documented reason R-005 remains High.</t>
   </si>
   <si>
-    <t xml:space="preserve">Implement a CIS CloudCo Foundations baseline with posture monitoring (Project 7 delivers this).</t>
+    <t xml:space="preserve">Implement a CIS AWS Foundations baseline with posture monitoring (Project 7 delivers this).</t>
   </si>
   <si>
     <t xml:space="preserve">REC-11</t>

--- a/06-soc2-readiness-internal-audit/06-soc2-readiness-and-internal-audit.xlsx
+++ b/06-soc2-readiness-internal-audit/06-soc2-readiness-and-internal-audit.xlsx
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Approved by</t>
   </si>
   <si>
-    <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer</t>
+    <t xml:space="preserve">Jerry Gold, Chief Executive Officer</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">2026-09-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Jerry Olugboye (CEO) - see OFI-08</t>
+    <t xml:space="preserve">Jerry Gold (CEO) - see OFI-08</t>
   </si>
   <si>
     <t xml:space="preserve">WP-02</t>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer</t>
+          <t xml:space="preserve">Jerry Gold, Chief Executive Officer</t>
         </is>
       </c>
     </row>
